--- a/artfynd/A 32217-2023 artfynd.xlsx
+++ b/artfynd/A 32217-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32217-2023 artfynd.xlsx
+++ b/artfynd/A 32217-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7130829</v>
+        <v>115429504</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Älggårdsberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590522.2308636956</v>
+        <v>590570</v>
       </c>
       <c r="R2" t="n">
-        <v>7007029.976378981</v>
+        <v>7007129</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-06-11</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-06-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,53 +760,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Askia Sandberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Askia Sandberg</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115429508</v>
+        <v>115429521</v>
       </c>
       <c r="B3" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590578</v>
+        <v>590526</v>
       </c>
       <c r="R3" t="n">
-        <v>7007105</v>
+        <v>7007131</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -897,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115429521</v>
+        <v>7130829</v>
       </c>
       <c r="B4" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,37 +880,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Älggårdsberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590526</v>
+        <v>590522</v>
       </c>
       <c r="R4" t="n">
-        <v>7007131</v>
+        <v>7007030</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,12 +938,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2013-06-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2013-06-11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,27 +958,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Askia Sandberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Askia Sandberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115429729</v>
+        <v>115429508</v>
       </c>
       <c r="B5" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,39 +985,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Älggårdsberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590579</v>
+        <v>590578</v>
       </c>
       <c r="R5" t="n">
-        <v>7007096</v>
+        <v>7007105</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1094,27 +1059,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115429733</v>
+        <v>115429509</v>
       </c>
       <c r="B6" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1146,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590572</v>
+        <v>590567</v>
       </c>
       <c r="R6" t="n">
-        <v>7007060</v>
+        <v>7007097</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1196,27 +1156,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115429519</v>
+        <v>115429510</v>
       </c>
       <c r="B7" t="n">
-        <v>55873</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1224,21 +1179,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1203,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590562</v>
+        <v>590499</v>
       </c>
       <c r="R7" t="n">
-        <v>7007066</v>
+        <v>7007001</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1310,15 +1265,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115429491</v>
+        <v>115429732</v>
       </c>
       <c r="B8" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1326,39 +1276,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Älggårdsberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590528</v>
+        <v>590599</v>
       </c>
       <c r="R8" t="n">
-        <v>7007013</v>
+        <v>7007081</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1405,27 +1350,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115429728</v>
+        <v>115429733</v>
       </c>
       <c r="B9" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1433,39 +1373,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Älggårdsberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590579</v>
+        <v>590572</v>
       </c>
       <c r="R9" t="n">
-        <v>7007123</v>
+        <v>7007060</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1524,53 +1459,64 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115429504</v>
+        <v>124690133</v>
       </c>
       <c r="B10" t="n">
-        <v>90615</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>besöker bebott bo</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Älggårdsberget, Ång</t>
+          <t>Helgum, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590570</v>
+        <v>590552</v>
       </c>
       <c r="R10" t="n">
-        <v>7007129</v>
+        <v>7007181</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1594,12 +1540,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1614,27 +1570,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115429732</v>
+        <v>115429491</v>
       </c>
       <c r="B11" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1642,34 +1593,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Älggårdsberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590599</v>
+        <v>590528</v>
       </c>
       <c r="R11" t="n">
-        <v>7007081</v>
+        <v>7007013</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1716,27 +1672,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115429509</v>
+        <v>115429727</v>
       </c>
       <c r="B12" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1744,34 +1695,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Älggårdsberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590567</v>
+        <v>590571</v>
       </c>
       <c r="R12" t="n">
-        <v>7007097</v>
+        <v>7007200</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1818,15 +1774,316 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>115429728</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Älggårdsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>590579</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7007123</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>115429729</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Älggårdsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>590579</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7007096</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>115429519</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Älggårdsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>590562</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7007066</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
           <t>Daniel Rutschman</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="AX15" t="inlineStr">
         <is>
           <t>Daniel Rutschman</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32217-2023 artfynd.xlsx
+++ b/artfynd/A 32217-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429504</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429521</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7130829</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429508</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,6 +1190,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429509</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1262,6 +1292,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429510</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1359,6 +1394,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429732</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1456,6 +1496,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429733</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1579,6 +1624,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124690133</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1681,6 +1731,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429491</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429727</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1885,6 +1945,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429728</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1987,6 +2052,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429729</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2084,8 +2154,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429519</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>